--- a/data/trans_dic/P12_3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,18</t>
+          <t>1,22; 3,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,72</t>
+          <t>2,81; 6,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,3</t>
+          <t>0,72; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,2</t>
+          <t>1,81; 9,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,72</t>
+          <t>3,47; 7,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,69</t>
+          <t>1,81; 5,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,36</t>
+          <t>3,23; 7,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 11,53</t>
+          <t>3,62; 12,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,01</t>
+          <t>2,61; 5,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,4</t>
+          <t>2,72; 5,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,67</t>
+          <t>2,18; 4,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,05</t>
+          <t>3,38; 8,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,8</t>
+          <t>2,01; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,04</t>
+          <t>3,16; 6,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,6</t>
+          <t>3,69; 7,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,93</t>
+          <t>5,32; 11,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,8</t>
+          <t>6,24; 10,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,18</t>
+          <t>4,14; 8,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,44</t>
+          <t>4,08; 8,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,24</t>
+          <t>5,59; 12,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,88</t>
+          <t>4,28; 6,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,93</t>
+          <t>4,17; 6,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,21</t>
+          <t>4,42; 7,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,11</t>
+          <t>6,33; 11,14</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,46</t>
+          <t>3,0; 6,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,54</t>
+          <t>4,62; 8,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,55</t>
+          <t>3,14; 6,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,57</t>
+          <t>5,6; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,64</t>
+          <t>4,93; 8,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,18</t>
+          <t>9,14; 13,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,1</t>
+          <t>4,24; 7,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,11</t>
+          <t>7,3; 11,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,14</t>
+          <t>4,46; 7,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,64</t>
+          <t>7,45; 10,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,57</t>
+          <t>4,06; 6,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,15</t>
+          <t>7,01; 10,05</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,85</t>
+          <t>2,88; 6,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,84</t>
+          <t>6,82; 12,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,3</t>
+          <t>8,24; 12,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,71</t>
+          <t>3,32; 12,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,54</t>
+          <t>6,42; 11,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 19,75</t>
+          <t>13,63; 19,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 13,72</t>
+          <t>9,0; 13,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,54</t>
+          <t>9,21; 13,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,48</t>
+          <t>5,08; 8,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 14,89</t>
+          <t>10,86; 14,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,71</t>
+          <t>9,08; 12,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,04</t>
+          <t>5,32; 12,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,1</t>
+          <t>4,73; 10,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,5</t>
+          <t>8,75; 14,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 13,82</t>
+          <t>7,86; 13,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 14,4</t>
+          <t>9,6; 14,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 12,65</t>
+          <t>6,91; 12,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 20,37</t>
+          <t>13,21; 20,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,73; 21,89</t>
+          <t>14,86; 22,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,95; 19,95</t>
+          <t>15,12; 19,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,29</t>
+          <t>6,41; 10,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 16,62</t>
+          <t>11,82; 16,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,82</t>
+          <t>12,09; 16,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,0; 16,62</t>
+          <t>12,95; 16,39</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,75</t>
+          <t>7,74; 14,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,1; 16,75</t>
+          <t>9,37; 17,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 10,82</t>
+          <t>4,82; 10,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,72; 16,42</t>
+          <t>10,95; 16,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 17,4</t>
+          <t>10,16; 17,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,99; 23,75</t>
+          <t>15,06; 23,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,45; 20,06</t>
+          <t>12,04; 20,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 19,11</t>
+          <t>5,52; 19,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,08</t>
+          <t>10,2; 15,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 18,88</t>
+          <t>13,24; 18,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,47</t>
+          <t>9,7; 14,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,85</t>
+          <t>6,95; 16,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 13,67</t>
+          <t>5,63; 13,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,6; 20,64</t>
+          <t>10,66; 19,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,75</t>
+          <t>11,37; 19,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,71</t>
+          <t>16,6; 24,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 15,11</t>
+          <t>7,64; 15,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,04; 30,18</t>
+          <t>21,2; 30,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,78</t>
+          <t>20,96; 31,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,37; 29,17</t>
+          <t>23,26; 29,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,0</t>
+          <t>7,8; 13,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,05; 24,69</t>
+          <t>17,95; 24,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,39; 25,34</t>
+          <t>18,35; 25,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,32; 26,03</t>
+          <t>21,48; 26,34</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1697,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,86</t>
+          <t>4,34; 5,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,11</t>
+          <t>7,12; 9,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,35</t>
+          <t>6,58; 8,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,34</t>
+          <t>7,69; 11,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,46</t>
+          <t>7,61; 9,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 14,52</t>
+          <t>12,05; 14,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,87</t>
+          <t>10,63; 12,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,39</t>
+          <t>10,52; 14,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,46</t>
+          <t>6,19; 7,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,34</t>
+          <t>8,91; 10,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 12,51</t>
+          <t>9,89; 12,49</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5830; 20654</t>
+          <t>6049; 19735</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13545; 30509</t>
+          <t>12751; 30145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2880; 13851</t>
+          <t>3021; 14953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7210; 36784</t>
+          <t>7226; 37167</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16567; 36106</t>
+          <t>16230; 34850</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8615; 24320</t>
+          <t>7749; 23060</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11891; 29079</t>
+          <t>12759; 30518</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11003; 36108</t>
+          <t>11340; 38095</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25359; 48166</t>
+          <t>25076; 48746</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24560; 47595</t>
+          <t>23980; 46576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17520; 38020</t>
+          <t>17777; 38400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23025; 64563</t>
+          <t>24117; 63023</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15111; 35312</t>
+          <t>14819; 35061</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24123; 48272</t>
+          <t>21679; 46880</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22500; 44876</t>
+          <t>21765; 43716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21432; 50537</t>
+          <t>22515; 50675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39181; 67534</t>
+          <t>39020; 67266</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24793; 49832</t>
+          <t>25248; 51751</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23907; 47541</t>
+          <t>22990; 45869</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26779; 62589</t>
+          <t>28587; 62520</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58750; 93580</t>
+          <t>58279; 94216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55873; 89761</t>
+          <t>53964; 89129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50076; 83203</t>
+          <t>51064; 83027</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57477; 103930</t>
+          <t>59176; 104184</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19376; 41261</t>
+          <t>19135; 41923</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31602; 58203</t>
+          <t>31519; 57886</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20846; 43817</t>
+          <t>21017; 43773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30785; 56717</t>
+          <t>30046; 55176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34149; 59585</t>
+          <t>33975; 60013</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64415; 100698</t>
+          <t>64881; 98318</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28158; 53343</t>
+          <t>27929; 51503</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39708; 60293</t>
+          <t>39583; 61081</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61523; 94882</t>
+          <t>59250; 92968</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103913; 148136</t>
+          <t>103675; 147820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53987; 87295</t>
+          <t>53941; 87133</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75911; 109547</t>
+          <t>75650; 108389</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15018; 35538</t>
+          <t>14972; 35457</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41605; 72332</t>
+          <t>41688; 73546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52964; 85659</t>
+          <t>53071; 83553</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29796; 112840</t>
+          <t>29514; 107198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32402; 59517</t>
+          <t>33087; 58715</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82238; 121476</t>
+          <t>83821; 122408</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57448; 89064</t>
+          <t>58394; 89963</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67329; 96341</t>
+          <t>65572; 95234</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54414; 87700</t>
+          <t>52540; 83682</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132724; 182529</t>
+          <t>133176; 182147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118604; 164390</t>
+          <t>117394; 165051</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>91210; 192667</t>
+          <t>85063; 196177</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19373; 39040</t>
+          <t>18299; 39371</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36389; 62261</t>
+          <t>37554; 64187</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38600; 65774</t>
+          <t>37384; 65613</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54349; 80403</t>
+          <t>53609; 81907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26641; 51085</t>
+          <t>27908; 49413</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58297; 91228</t>
+          <t>59149; 91638</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72840; 108251</t>
+          <t>73497; 110327</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81816; 109154</t>
+          <t>82737; 109315</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51124; 81370</t>
+          <t>50646; 82790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103295; 145820</t>
+          <t>103666; 146083</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116621; 163263</t>
+          <t>117344; 163457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>143703; 183768</t>
+          <t>143173; 181215</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22299; 43149</t>
+          <t>22637; 43486</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28179; 51904</t>
+          <t>29033; 52779</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16722; 36070</t>
+          <t>16060; 35746</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39484; 60447</t>
+          <t>40315; 61849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35567; 59682</t>
+          <t>34852; 60762</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53069; 84079</t>
+          <t>53295; 83384</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47026; 75762</t>
+          <t>45474; 76867</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28520; 116264</t>
+          <t>33603; 117699</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>63806; 95861</t>
+          <t>64853; 96185</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87181; 125307</t>
+          <t>87866; 124650</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67421; 102883</t>
+          <t>68983; 103074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65382; 164567</t>
+          <t>67833; 164824</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11607; 28695</t>
+          <t>11814; 28847</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26393; 51371</t>
+          <t>26539; 48555</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29088; 50768</t>
+          <t>29226; 49750</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47015; 66922</t>
+          <t>46853; 68030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25729; 50453</t>
+          <t>25523; 50592</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81859; 117382</t>
+          <t>82467; 117291</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84575; 122788</t>
+          <t>83594; 123764</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>99124; 123734</t>
+          <t>98681; 123376</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42680; 70689</t>
+          <t>42437; 72830</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115163; 157485</t>
+          <t>114484; 155967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120589; 166184</t>
+          <t>120378; 164433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>150611; 183901</t>
+          <t>151764; 186078</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>143463; 192159</t>
+          <t>142339; 191186</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>244051; 311769</t>
+          <t>243438; 310899</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>219954; 282827</t>
+          <t>222906; 283150</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>261632; 391794</t>
+          <t>265822; 386179</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>254823; 319623</t>
+          <t>257068; 322135</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>429410; 515675</t>
+          <t>428105; 514007</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>377743; 455323</t>
+          <t>376179; 454713</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>383620; 526372</t>
+          <t>384807; 527633</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>413707; 496793</t>
+          <t>411795; 487619</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>697227; 802929</t>
+          <t>697074; 802675</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>617461; 715912</t>
+          <t>617307; 712009</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>721084; 889857</t>
+          <t>704016; 888582</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,99</t>
+          <t>1,19; 4,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,64</t>
+          <t>2,84; 6,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,56</t>
+          <t>0,65; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,29</t>
+          <t>2,54; 10,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,45</t>
+          <t>3,49; 7,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,4</t>
+          <t>1,64; 5,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,73</t>
+          <t>2,95; 7,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,16</t>
+          <t>3,57; 11,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,07</t>
+          <t>2,57; 5,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,28</t>
+          <t>2,7; 5,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,72</t>
+          <t>2,11; 4,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,84</t>
+          <t>3,83; 9,16</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,77</t>
+          <t>2,11; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,83</t>
+          <t>3,44; 6,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,4</t>
+          <t>3,61; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 11,96</t>
+          <t>5,74; 12,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,75</t>
+          <t>6,1; 10,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,5</t>
+          <t>4,17; 8,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,14</t>
+          <t>4,21; 8,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 12,22</t>
+          <t>8,05; 14,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,92</t>
+          <t>4,36; 6,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,88</t>
+          <t>4,31; 6,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,19</t>
+          <t>4,35; 7,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,14</t>
+          <t>7,79; 12,24</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,56</t>
+          <t>3,11; 6,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,49</t>
+          <t>4,6; 8,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,54</t>
+          <t>3,11; 6,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,29</t>
+          <t>5,48; 9,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,7</t>
+          <t>4,88; 8,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,85</t>
+          <t>8,83; 13,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,82</t>
+          <t>4,23; 7,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,26</t>
+          <t>7,97; 12,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,0</t>
+          <t>4,45; 6,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,62</t>
+          <t>7,45; 10,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,56</t>
+          <t>4,18; 6,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,05</t>
+          <t>7,34; 10,32</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,83</t>
+          <t>2,97; 6,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 12,04</t>
+          <t>6,83; 11,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,98</t>
+          <t>8,13; 13,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 12,07</t>
+          <t>7,85; 12,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,39</t>
+          <t>6,42; 11,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 19,9</t>
+          <t>13,48; 19,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,86</t>
+          <t>8,61; 13,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,38</t>
+          <t>10,25; 14,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,09</t>
+          <t>5,21; 8,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,86</t>
+          <t>10,98; 14,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 12,77</t>
+          <t>9,2; 12,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,26</t>
+          <t>9,63; 12,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,18</t>
+          <t>4,8; 9,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,75; 14,95</t>
+          <t>8,52; 15,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 13,79</t>
+          <t>7,82; 13,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,67</t>
+          <t>9,73; 14,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 12,23</t>
+          <t>6,58; 12,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,21; 20,46</t>
+          <t>13,18; 20,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,86; 22,31</t>
+          <t>15,04; 22,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 19,98</t>
+          <t>15,34; 20,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,47</t>
+          <t>6,38; 10,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,65</t>
+          <t>11,57; 16,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,84</t>
+          <t>12,18; 16,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 16,39</t>
+          <t>13,28; 16,7</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 14,86</t>
+          <t>7,53; 14,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,04</t>
+          <t>8,45; 17,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,72</t>
+          <t>4,78; 10,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 16,8</t>
+          <t>11,0; 16,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,16; 17,72</t>
+          <t>10,32; 17,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,06; 23,55</t>
+          <t>14,84; 23,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,04; 20,35</t>
+          <t>11,98; 19,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 19,35</t>
+          <t>16,62; 22,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,2; 15,13</t>
+          <t>10,02; 14,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,78</t>
+          <t>13,34; 19,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,49</t>
+          <t>9,62; 14,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,95; 16,88</t>
+          <t>14,51; 18,44</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 13,74</t>
+          <t>5,4; 12,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,66; 19,51</t>
+          <t>10,68; 19,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 19,36</t>
+          <t>11,63; 20,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,6; 24,1</t>
+          <t>16,71; 24,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 15,15</t>
+          <t>7,56; 14,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,15</t>
+          <t>20,85; 30,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,96; 31,03</t>
+          <t>20,68; 30,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,26; 29,09</t>
+          <t>23,8; 29,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,39</t>
+          <t>7,8; 13,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,95; 24,45</t>
+          <t>18,04; 24,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,35; 25,07</t>
+          <t>18,15; 24,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,48; 26,34</t>
+          <t>21,72; 26,65</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,83</t>
+          <t>4,37; 5,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,09</t>
+          <t>7,17; 9,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,35</t>
+          <t>6,47; 8,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,17</t>
+          <t>9,49; 11,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,53</t>
+          <t>7,6; 9,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,05; 14,47</t>
+          <t>12,15; 14,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,63; 12,85</t>
+          <t>10,65; 12,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,42</t>
+          <t>13,59; 15,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,33</t>
+          <t>6,24; 7,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,0; 11,51</t>
+          <t>9,97; 11,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,28</t>
+          <t>8,85; 10,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,49</t>
+          <t>11,9; 13,37</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39354</t>
+          <t>46133</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6049; 19735</t>
+          <t>5888; 20425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12751; 30145</t>
+          <t>12882; 30365</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3021; 14953</t>
+          <t>2712; 14467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7226; 37167</t>
+          <t>10341; 42987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16230; 34850</t>
+          <t>16297; 35374</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7749; 23060</t>
+          <t>6992; 23845</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12759; 30518</t>
+          <t>11639; 28363</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11340; 38095</t>
+          <t>12958; 40579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25076; 48746</t>
+          <t>24668; 48058</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23980; 46576</t>
+          <t>23840; 46944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17777; 38400</t>
+          <t>17153; 38706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24117; 63023</t>
+          <t>29472; 70542</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35115</t>
+          <t>41352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>53614</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80413</t>
+          <t>94966</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14819; 35061</t>
+          <t>15549; 35055</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21679; 46880</t>
+          <t>23578; 47831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21765; 43716</t>
+          <t>21317; 43487</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22515; 50675</t>
+          <t>27386; 58111</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39020; 67266</t>
+          <t>38162; 66824</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25248; 51751</t>
+          <t>25414; 49953</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22990; 45869</t>
+          <t>23741; 46413</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28587; 62520</t>
+          <t>40357; 70590</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58279; 94216</t>
+          <t>59278; 93716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53964; 89129</t>
+          <t>55843; 89893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51064; 83027</t>
+          <t>50252; 81288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59176; 104184</t>
+          <t>76197; 119691</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41730</t>
+          <t>46972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49713</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91443</t>
+          <t>108516</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19135; 41923</t>
+          <t>19875; 40994</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31519; 57886</t>
+          <t>31353; 57513</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21017; 43773</t>
+          <t>20802; 43778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30046; 55176</t>
+          <t>34053; 60976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33975; 60013</t>
+          <t>33631; 61325</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64881; 98318</t>
+          <t>62671; 99291</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27929; 51503</t>
+          <t>27867; 52199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39583; 61081</t>
+          <t>49554; 76021</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59250; 92968</t>
+          <t>59058; 92664</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103675; 147820</t>
+          <t>103629; 148775</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53941; 87133</t>
+          <t>55477; 87383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75650; 108389</t>
+          <t>91223; 128243</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71861</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81769</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>153630</t>
+          <t>159961</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14972; 35457</t>
+          <t>15436; 35827</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41688; 73546</t>
+          <t>41714; 70770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53071; 83553</t>
+          <t>52364; 86862</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29514; 107198</t>
+          <t>55006; 88110</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33087; 58715</t>
+          <t>33092; 58523</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83821; 122408</t>
+          <t>82957; 121432</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58394; 89963</t>
+          <t>55894; 89229</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65572; 95234</t>
+          <t>75421; 105473</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52540; 83682</t>
+          <t>53951; 87920</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>133176; 182147</t>
+          <t>134599; 183619</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117394; 165051</t>
+          <t>118923; 162642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85063; 196177</t>
+          <t>138338; 183428</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>73284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>95005</t>
+          <t>108466</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>161724</t>
+          <t>181750</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18299; 39371</t>
+          <t>18559; 38183</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37554; 64187</t>
+          <t>36577; 64599</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37384; 65613</t>
+          <t>37204; 64876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53609; 81907</t>
+          <t>58949; 90043</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27908; 49413</t>
+          <t>26599; 50852</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59149; 91638</t>
+          <t>59028; 93380</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73497; 110327</t>
+          <t>74394; 110569</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82737; 109315</t>
+          <t>93274; 123448</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50646; 82790</t>
+          <t>50443; 80894</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103666; 146083</t>
+          <t>101515; 143570</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117344; 163457</t>
+          <t>118229; 163430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>143173; 181215</t>
+          <t>161295; 202782</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>54965</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>73981</t>
+          <t>84920</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>124033</t>
+          <t>139885</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22637; 43486</t>
+          <t>22040; 43773</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29033; 52779</t>
+          <t>26165; 52869</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16060; 35746</t>
+          <t>15920; 36061</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40315; 61849</t>
+          <t>44789; 67122</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34852; 60762</t>
+          <t>35397; 60585</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53295; 83384</t>
+          <t>52531; 83018</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45474; 76867</t>
+          <t>45266; 74765</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>33603; 117699</t>
+          <t>73003; 96600</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64853; 96185</t>
+          <t>63699; 94642</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87866; 124650</t>
+          <t>88546; 129403</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68983; 103074</t>
+          <t>68440; 103701</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67833; 164824</t>
+          <t>122807; 156053</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56419</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>110647</t>
+          <t>123257</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>167066</t>
+          <t>186759</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11814; 28847</t>
+          <t>11324; 27135</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26539; 48555</t>
+          <t>26573; 48417</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29226; 49750</t>
+          <t>29899; 51852</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46853; 68030</t>
+          <t>51753; 75426</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25523; 50592</t>
+          <t>25255; 48828</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>82467; 117291</t>
+          <t>81104; 117441</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83594; 123764</t>
+          <t>82507; 123520</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>98681; 123376</t>
+          <t>110190; 138712</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42437; 72830</t>
+          <t>42429; 70750</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114484; 155967</t>
+          <t>115067; 158306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120378; 164433</t>
+          <t>119025; 163701</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>151764; 186078</t>
+          <t>167814; 205911</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>339395</t>
+          <t>372171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>478268</t>
+          <t>545799</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>817663</t>
+          <t>917970</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>142339; 191186</t>
+          <t>143211; 193234</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>243438; 310899</t>
+          <t>245231; 309431</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>222906; 283150</t>
+          <t>219243; 281575</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>265822; 386179</t>
+          <t>334899; 414889</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>257068; 322135</t>
+          <t>256718; 323281</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>428105; 514007</t>
+          <t>431634; 516370</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>376179; 454713</t>
+          <t>376754; 457968</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>384807; 527633</t>
+          <t>507321; 582410</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>411795; 487619</t>
+          <t>415159; 501040</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>697074; 802675</t>
+          <t>695485; 802469</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>617307; 712009</t>
+          <t>613129; 715991</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>704016; 888582</t>
+          <t>863725; 971068</t>
         </is>
       </c>
     </row>
